--- a/output/laminas_comunales/comunal_o_ocup_a_2023_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2023_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,97 +384,832 @@
         </is>
       </c>
       <c r="C2">
-        <v>39.3079019847242</v>
+        <v>55.0729115175482</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C3">
-        <v>38.7610106743394</v>
+        <v>53.5935153773427</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="C4">
-        <v>36.3992000561364</v>
+        <v>52.3281726483697</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C5">
-        <v>33.339591938916</v>
+        <v>51.6922893576451</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C6">
-        <v>26.6622340425532</v>
+        <v>51.0740807552389</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colchane</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C7">
-        <v>26.5178571428571</v>
+        <v>49.642499119456</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>49.3560345486509</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>46.6220269433755</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>46.0523176931908</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>45.6840916424653</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>44.8942855583322</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>43.871376647322</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>42.877094972067</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>42.7525220547887</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>41.9811320754717</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>39.3079019847242</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>39.1075206528309</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>38.88</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>38.7610106743394</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>37.6704545454545</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>37.060254491018</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>1402</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Camiña</t>
         </is>
       </c>
-      <c r="C8">
+      <c r="C23">
+        <v>36.6336633663366</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>36.3992000561364</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>34.7260946918399</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>33.339591938916</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>33.1950617463562</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>32.4000957166786</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>32.0703907815631</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>31.957657007106</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>31.2957533639185</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>30.7916696554527</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>30.4826948924731</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>30.3589743589744</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>29.7417442845047</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>29.5936950514946</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>28.5030427027594</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>27.8625954198473</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>27.6721014492754</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>26.6622340425532</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>26.5178571428571</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>25.0631313131313</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>25.0394944707741</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>25.0355366027008</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>24.1984521835268</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>23.2790697674419</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C47">
         <v>21.8447441217151</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>21.2056737588652</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>18.8215488215488</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>14.7255002565418</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>13.4540282453989</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>12.9943914502738</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>12.4984630517644</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>8.54655294953802</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>8.39307048984468</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>6.0882800608828</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>3.83928571428571</v>
       </c>
     </row>
   </sheetData>
